--- a/Figure 5.xlsx
+++ b/Figure 5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/907e8644eb03ffa4/바탕 화면/@연구실/_논문 작성/figure set/raw data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/907e8644eb03ffa4/바탕 화면/@연구실/_논문 작성/@@PNAS 리비전/@@@proof/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6803131-020B-4511-985E-6578A94077AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{F6803131-020B-4511-985E-6578A94077AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACD33241-A6D2-4A4F-8892-E525A5C21039}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{504A17AC-85B6-4785-A9B6-8320E24DF010}"/>
+    <workbookView xWindow="225" yWindow="1200" windowWidth="29010" windowHeight="13530" activeTab="2" xr2:uid="{504A17AC-85B6-4785-A9B6-8320E24DF010}"/>
   </bookViews>
   <sheets>
     <sheet name="fig5b" sheetId="2" r:id="rId1"/>
@@ -104,7 +104,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +117,14 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -143,11 +151,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -165,10 +176,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -492,388 +499,401 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>-1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>6</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>8</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>10</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>12</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>17</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>24</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>30</v>
       </c>
     </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>1</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-2.0889999999999999E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7.2100000000000003E-3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.12909999999999999</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.28799000000000002</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.37028</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.26816000000000001</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.19375000000000001</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.17343</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.11562</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.043E-2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2.9090000000000001E-2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.13911999999999999</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.25758999999999999</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.19145000000000001</v>
+      </c>
+      <c r="H8" s="1">
+        <v>2.7869999999999999E-2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5.5549899999999999E-4</v>
+      </c>
+      <c r="J8" s="1">
+        <v>-3.4009999999999999E-2</v>
+      </c>
+      <c r="K8" s="1">
+        <v>-6.3280000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2.4E-2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4.394E-2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.15978000000000001</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.30456</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.35241</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.27623999999999999</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.18043999999999999</v>
+      </c>
+      <c r="J9" s="1">
+        <v>4.394E-2</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1.196E-2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4.0160000000000001E-2</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4.5859999999999998E-2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.26690000000000003</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.33149000000000001</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.41132999999999997</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.35160999999999998</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.34405999999999998</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.29558000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>7.7299999999999999E-3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>3.9940000000000003E-2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.28705999999999998</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.32340000000000002</v>
+      </c>
+      <c r="G11" s="1">
+        <v>7.0180000000000006E-2</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.15981999999999999</v>
+      </c>
+      <c r="I11" s="1">
+        <v>7.0180000000000006E-2</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.10543</v>
+      </c>
+      <c r="K11" s="1">
+        <v>6.6769999999999996E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.1729999999999999E-2</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.12278</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.16744000000000001</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.26284999999999997</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3.3430000000000001E-2</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.10921</v>
+      </c>
+      <c r="K12" s="1">
+        <v>-8.2570000000000005E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
         <v>-5.8369999999999998E-2</v>
       </c>
-      <c r="D7">
+      <c r="D13" s="1">
         <v>-3.524E-2</v>
       </c>
-      <c r="E7">
+      <c r="E13" s="1">
         <v>3.3430000000000001E-2</v>
       </c>
-      <c r="F7">
+      <c r="F13" s="1">
         <v>0.13533000000000001</v>
       </c>
-      <c r="G7">
+      <c r="G13" s="1">
         <v>0.18790000000000001</v>
       </c>
-      <c r="H7">
+      <c r="H13" s="1">
         <v>0.32602999999999999</v>
       </c>
-      <c r="I7">
-        <v>0.26284999999999997</v>
-      </c>
-      <c r="J7">
+      <c r="I13" s="2">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="J13" s="1">
         <v>0.13533000000000001</v>
       </c>
-      <c r="K7">
+      <c r="K13" s="1">
         <v>0.21567</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>-2.0889999999999999E-2</v>
-      </c>
-      <c r="D8">
-        <v>7.2100000000000003E-3</v>
-      </c>
-      <c r="E8">
-        <v>0.12909999999999999</v>
-      </c>
-      <c r="F8">
-        <v>0.28799000000000002</v>
-      </c>
-      <c r="G8">
-        <v>0.37028</v>
-      </c>
-      <c r="H8">
-        <v>0.26816000000000001</v>
-      </c>
-      <c r="I8">
-        <v>0.19375000000000001</v>
-      </c>
-      <c r="J8">
-        <v>0.17343</v>
-      </c>
-      <c r="K8">
-        <v>0.11562</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="D9">
+      <c r="D14" s="1">
         <v>4.5859999999999998E-2</v>
       </c>
-      <c r="E9">
+      <c r="E14" s="1">
         <v>0.33149000000000001</v>
       </c>
-      <c r="F9">
+      <c r="F14" s="1">
         <v>0.41132999999999997</v>
       </c>
-      <c r="G9">
+      <c r="G14" s="1">
         <v>0.34405999999999998</v>
       </c>
-      <c r="H9">
+      <c r="H14" s="1">
         <v>0.29558000000000001</v>
       </c>
-      <c r="I9">
+      <c r="I14" s="1">
         <v>0.19825000000000001</v>
       </c>
-      <c r="J9">
+      <c r="J14" s="1">
         <v>0.10329000000000001</v>
       </c>
-      <c r="K9">
+      <c r="K14" s="1">
         <v>4.5859999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>4</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>7.7299999999999999E-3</v>
-      </c>
-      <c r="D10">
-        <v>3.9940000000000003E-2</v>
-      </c>
-      <c r="E10">
-        <v>0.28705999999999998</v>
-      </c>
-      <c r="F10">
-        <v>0.32340000000000002</v>
-      </c>
-      <c r="G10">
-        <v>7.0180000000000006E-2</v>
-      </c>
-      <c r="H10">
-        <v>0.15981999999999999</v>
-      </c>
-      <c r="I10">
-        <v>7.0180000000000006E-2</v>
-      </c>
-      <c r="J10">
-        <v>0.10543</v>
-      </c>
-      <c r="K10">
-        <v>6.6769999999999996E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>5</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>2.4E-2</v>
-      </c>
-      <c r="D11">
-        <v>4.394E-2</v>
-      </c>
-      <c r="E11">
-        <v>0.15978000000000001</v>
-      </c>
-      <c r="F11">
-        <v>0.30456</v>
-      </c>
-      <c r="G11">
-        <v>0.35241</v>
-      </c>
-      <c r="H11">
-        <v>0.27623999999999999</v>
-      </c>
-      <c r="I11">
-        <v>0.18043999999999999</v>
-      </c>
-      <c r="J11">
-        <v>4.394E-2</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>6</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>1.196E-2</v>
-      </c>
-      <c r="D12">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="D15" s="1">
         <v>4.0160000000000001E-2</v>
       </c>
-      <c r="E12">
-        <v>4.5859999999999998E-2</v>
-      </c>
-      <c r="F12">
-        <v>0.26690000000000003</v>
-      </c>
-      <c r="G12">
+      <c r="E15" s="1">
+        <v>0.14893999999999999</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.26606000000000002</v>
+      </c>
+      <c r="G15" s="1">
         <v>0.33149000000000001</v>
       </c>
-      <c r="H12">
-        <v>0.41132999999999997</v>
-      </c>
-      <c r="I12">
-        <v>0.35160999999999998</v>
-      </c>
-      <c r="J12">
-        <v>0.34405999999999998</v>
-      </c>
-      <c r="K12">
+      <c r="H15" s="1">
         <v>0.29558000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>7</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>2.043E-2</v>
-      </c>
-      <c r="D13">
-        <v>2.9090000000000001E-2</v>
-      </c>
-      <c r="E13">
-        <v>0.13911999999999999</v>
-      </c>
-      <c r="F13">
-        <v>0.25758999999999999</v>
-      </c>
-      <c r="G13">
-        <v>0.19145000000000001</v>
-      </c>
-      <c r="H13">
-        <v>2.7869999999999999E-2</v>
-      </c>
-      <c r="I13" s="1">
-        <v>5.5549899999999999E-4</v>
-      </c>
-      <c r="J13">
-        <v>-3.4009999999999999E-2</v>
-      </c>
-      <c r="K13">
-        <v>-6.3280000000000003E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>8</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>3.1600000000000003E-2</v>
-      </c>
-      <c r="D14">
+      <c r="I15" s="1">
+        <v>0.16986000000000001</v>
+      </c>
+      <c r="J15" s="1">
         <v>4.0160000000000001E-2</v>
       </c>
-      <c r="E14">
-        <v>0.14893999999999999</v>
-      </c>
-      <c r="F14">
-        <v>0.26606000000000002</v>
-      </c>
-      <c r="G14">
-        <v>0.33149000000000001</v>
-      </c>
-      <c r="H14">
-        <v>0.29558000000000001</v>
-      </c>
-      <c r="I14">
-        <v>0.16986000000000001</v>
-      </c>
-      <c r="J14">
-        <v>4.0160000000000001E-2</v>
-      </c>
-      <c r="K14">
+      <c r="K15" s="1">
         <v>-2.222E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>9</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
         <v>-2.1389999999999999E-2</v>
       </c>
-      <c r="D15">
+      <c r="D16" s="1">
         <v>-4.7999999999999996E-3</v>
       </c>
-      <c r="E15">
+      <c r="E16" s="1">
         <v>3.934E-2</v>
       </c>
-      <c r="F15">
+      <c r="F16" s="1">
         <v>0.20466000000000001</v>
       </c>
-      <c r="G15">
+      <c r="G16" s="1">
         <v>9.6699999999999994E-2</v>
       </c>
-      <c r="H15">
+      <c r="H16" s="1">
         <v>-1.404E-2</v>
       </c>
-      <c r="I15">
+      <c r="I16" s="1">
         <v>-0.15123</v>
       </c>
-      <c r="J15">
+      <c r="J16" s="1">
         <v>-7.3219999999999993E-2</v>
       </c>
-      <c r="K15">
+      <c r="K16" s="1">
         <v>-9.7769999999999996E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>10</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>2.1729999999999999E-2</v>
-      </c>
-      <c r="D16">
-        <v>4.0899999999999999E-2</v>
-      </c>
-      <c r="E16">
-        <v>0.12278</v>
-      </c>
-      <c r="F16">
-        <v>0.16744000000000001</v>
-      </c>
-      <c r="G16">
-        <v>0.26284999999999997</v>
-      </c>
-      <c r="H16">
-        <v>3.3430000000000001E-2</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0.10921</v>
-      </c>
-      <c r="K16">
-        <v>-8.2570000000000005E-2</v>
       </c>
     </row>
   </sheetData>
@@ -972,497 +992,539 @@
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H3" t="s">
+      <c r="G3" s="1"/>
+      <c r="H3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J3" t="s">
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L3" t="s">
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N3" t="s">
+      <c r="M3" s="1"/>
+      <c r="N3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P3" t="s">
+      <c r="O3" s="1"/>
+      <c r="P3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R3" t="s">
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T3" t="s">
+      <c r="S3" s="1"/>
+      <c r="T3" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="G4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
         <v>-13</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1.81E-3</v>
       </c>
-      <c r="M4">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1">
         <v>-13</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>0.13957</v>
       </c>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E5">
+      <c r="A5" s="1">
         <v>-11</v>
       </c>
-      <c r="F5">
+      <c r="B5" s="1">
+        <v>0.16095000000000001</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1">
+        <v>-11</v>
+      </c>
+      <c r="F5" s="1">
         <v>0.14963000000000001</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>-11</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>1.5200000000000001E-3</v>
       </c>
-      <c r="K5">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1">
         <v>-11</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>5.2760000000000001E-2</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-11</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>4.138E-2</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1">
         <v>-11</v>
       </c>
-      <c r="P5">
-        <v>0.16095000000000001</v>
-      </c>
-      <c r="S5">
-        <v>-11</v>
-      </c>
-      <c r="T5">
+      <c r="R5" s="1">
         <v>0.21640000000000001</v>
       </c>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E6">
+      <c r="A6" s="1">
         <v>-9</v>
       </c>
-      <c r="F6">
+      <c r="B6" s="1">
+        <v>1.97E-3</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1">
+        <v>-9</v>
+      </c>
+      <c r="F6" s="1">
         <v>2.5100000000000001E-3</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>-9</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>2.65E-3</v>
       </c>
-      <c r="K6">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1">
         <v>-9</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>1.204E-2</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-9</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>0.16072</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1">
         <v>-9</v>
       </c>
-      <c r="P6">
-        <v>1.97E-3</v>
-      </c>
-      <c r="S6">
-        <v>-9</v>
-      </c>
-      <c r="T6" s="1">
+      <c r="R6" s="1">
         <v>1.223E-2</v>
       </c>
+      <c r="S6" s="1"/>
+      <c r="T6" s="2"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>-8</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
+        <v>1.413E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1.3600000000000001E-3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2.5610000000000001E-2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="H7" s="2">
+        <v>6.0999999999999997E-4</v>
+      </c>
+      <c r="I7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="J7" s="1">
+        <v>3.0849999999999999E-2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="L7" s="1">
+        <v>5.6600000000000001E-3</v>
+      </c>
+      <c r="M7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0.68594999999999995</v>
+      </c>
+      <c r="O7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="P7" s="1">
+        <v>2.87E-2</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="R7" s="1">
+        <v>3.5300000000000002E-3</v>
+      </c>
+      <c r="S7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="T7" s="1">
         <v>2.3019999999999999E-2</v>
       </c>
-      <c r="C7">
-        <v>-8</v>
-      </c>
-      <c r="D7">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>3.56E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1.25E-3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.10647</v>
+      </c>
+      <c r="G8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="J8" s="1">
+        <v>3.1879999999999999E-2</v>
+      </c>
+      <c r="K8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1.7600000000000001E-3</v>
+      </c>
+      <c r="M8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0.59909999999999997</v>
+      </c>
+      <c r="O8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1.5221999999999999E-5</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="R8" s="2">
+        <v>9.2799999999999994E-2</v>
+      </c>
+      <c r="S8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="T8" s="1">
+        <v>3.3705699999999998E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>9.1370000000000007E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2.2399999999999998E-3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.29748000000000002</v>
+      </c>
+      <c r="G9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.26584999999999998</v>
+      </c>
+      <c r="I9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2.2210000000000001E-2</v>
+      </c>
+      <c r="K9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2.92E-2</v>
+      </c>
+      <c r="M9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.56072</v>
+      </c>
+      <c r="O9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="P9" s="1">
         <v>1.3600000000000001E-3</v>
       </c>
-      <c r="E7">
-        <v>-8</v>
-      </c>
-      <c r="F7">
-        <v>2.5610000000000001E-2</v>
-      </c>
-      <c r="G7">
-        <v>-8</v>
-      </c>
-      <c r="H7" s="1">
-        <v>6.0997600000000003E-4</v>
-      </c>
-      <c r="I7">
-        <v>-8</v>
-      </c>
-      <c r="J7">
-        <v>3.0849999999999999E-2</v>
-      </c>
-      <c r="K7">
-        <v>-8</v>
-      </c>
-      <c r="L7">
-        <v>5.6600000000000001E-3</v>
-      </c>
-      <c r="M7">
-        <v>-8</v>
-      </c>
-      <c r="N7">
-        <v>0.68594999999999995</v>
-      </c>
-      <c r="O7">
-        <v>-8</v>
-      </c>
-      <c r="P7">
-        <v>1.413E-2</v>
-      </c>
-      <c r="Q7">
-        <v>-8</v>
-      </c>
-      <c r="R7">
-        <v>2.87E-2</v>
-      </c>
-      <c r="S7">
-        <v>-8</v>
-      </c>
-      <c r="T7">
-        <v>3.5300000000000002E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>-7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3.3705699999999998E-4</v>
-      </c>
-      <c r="C8">
-        <v>-7</v>
-      </c>
-      <c r="D8">
-        <v>1.25E-3</v>
-      </c>
-      <c r="E8">
-        <v>-7</v>
-      </c>
-      <c r="F8">
-        <v>0.10647</v>
-      </c>
-      <c r="G8">
-        <v>-7</v>
-      </c>
-      <c r="H8">
-        <v>1.1299999999999999E-2</v>
-      </c>
-      <c r="I8">
-        <v>-7</v>
-      </c>
-      <c r="J8">
-        <v>3.1879999999999999E-2</v>
-      </c>
-      <c r="K8">
-        <v>-7</v>
-      </c>
-      <c r="L8">
-        <v>1.7600000000000001E-3</v>
-      </c>
-      <c r="M8">
-        <v>-7</v>
-      </c>
-      <c r="N8">
-        <v>0.59909999999999997</v>
-      </c>
-      <c r="O8">
-        <v>-7</v>
-      </c>
-      <c r="P8">
-        <v>3.5569999999999997E-2</v>
-      </c>
-      <c r="Q8">
-        <v>-7</v>
-      </c>
-      <c r="R8" s="1">
-        <v>1.5221999999999999E-5</v>
-      </c>
-      <c r="S8">
-        <v>-7</v>
-      </c>
-      <c r="T8">
-        <v>9.2840000000000006E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="Q9" s="1">
         <v>-6</v>
       </c>
-      <c r="B9">
+      <c r="R9" s="1">
+        <v>0.16422</v>
+      </c>
+      <c r="S9" s="1">
+        <v>-6</v>
+      </c>
+      <c r="T9" s="1">
         <v>5.5599999999999998E-3</v>
       </c>
-      <c r="C9">
-        <v>-6</v>
-      </c>
-      <c r="D9">
-        <v>2.2399999999999998E-3</v>
-      </c>
-      <c r="E9">
-        <v>-6</v>
-      </c>
-      <c r="F9">
-        <v>0.29748000000000002</v>
-      </c>
-      <c r="G9">
-        <v>-6</v>
-      </c>
-      <c r="H9">
-        <v>0.26584999999999998</v>
-      </c>
-      <c r="I9">
-        <v>-6</v>
-      </c>
-      <c r="J9">
-        <v>2.2210000000000001E-2</v>
-      </c>
-      <c r="K9">
-        <v>-6</v>
-      </c>
-      <c r="L9">
-        <v>2.92E-2</v>
-      </c>
-      <c r="M9">
-        <v>-6</v>
-      </c>
-      <c r="N9">
-        <v>0.56072</v>
-      </c>
-      <c r="O9">
-        <v>-6</v>
-      </c>
-      <c r="P9">
-        <v>9.1370000000000007E-2</v>
-      </c>
-      <c r="Q9">
-        <v>-6</v>
-      </c>
-      <c r="R9">
-        <v>1.3600000000000001E-3</v>
-      </c>
-      <c r="S9">
-        <v>-6</v>
-      </c>
-      <c r="T9">
-        <v>0.16422</v>
-      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>-4</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
+        <v>0.32366</v>
+      </c>
+      <c r="C10" s="1">
+        <v>-4</v>
+      </c>
+      <c r="D10" s="1">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-4</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.42723</v>
+      </c>
+      <c r="G10" s="1">
+        <v>-4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.86434999999999995</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-4</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2.911E-2</v>
+      </c>
+      <c r="K10" s="1">
+        <v>-4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0.3004</v>
+      </c>
+      <c r="M10" s="1">
+        <v>-4</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0.85697000000000001</v>
+      </c>
+      <c r="O10" s="1">
+        <v>-4</v>
+      </c>
+      <c r="P10" s="1">
+        <v>5.3699999999999998E-3</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>-4</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0.44296999999999997</v>
+      </c>
+      <c r="S10" s="1">
+        <v>-4</v>
+      </c>
+      <c r="T10" s="1">
         <v>9.7300000000000008E-3</v>
       </c>
-      <c r="C10">
-        <v>-4</v>
-      </c>
-      <c r="D10">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="E10">
-        <v>-4</v>
-      </c>
-      <c r="F10">
-        <v>0.42723</v>
-      </c>
-      <c r="G10">
-        <v>-4</v>
-      </c>
-      <c r="H10">
-        <v>0.86434999999999995</v>
-      </c>
-      <c r="I10">
-        <v>-4</v>
-      </c>
-      <c r="J10">
-        <v>2.911E-2</v>
-      </c>
-      <c r="K10">
-        <v>-4</v>
-      </c>
-      <c r="L10">
-        <v>0.3004</v>
-      </c>
-      <c r="M10">
-        <v>-4</v>
-      </c>
-      <c r="N10">
-        <v>0.85697000000000001</v>
-      </c>
-      <c r="O10">
-        <v>-4</v>
-      </c>
-      <c r="P10">
-        <v>0.32366</v>
-      </c>
-      <c r="Q10">
-        <v>-4</v>
-      </c>
-      <c r="R10">
-        <v>5.3699999999999998E-3</v>
-      </c>
-      <c r="S10">
-        <v>-4</v>
-      </c>
-      <c r="T10">
-        <v>0.44296999999999997</v>
-      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>-2</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
+        <v>0.78354000000000001</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>8.616E-2</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.86656999999999995</v>
+      </c>
+      <c r="G11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.99475999999999998</v>
+      </c>
+      <c r="I11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.12747</v>
+      </c>
+      <c r="K11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0.82855999999999996</v>
+      </c>
+      <c r="M11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0.95130999999999999</v>
+      </c>
+      <c r="O11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0.26454</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0.91578000000000004</v>
+      </c>
+      <c r="S11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="T11" s="1">
         <v>0.51575000000000004</v>
       </c>
-      <c r="C11">
-        <v>-2</v>
-      </c>
-      <c r="D11">
-        <v>8.616E-2</v>
-      </c>
-      <c r="E11">
-        <v>-2</v>
-      </c>
-      <c r="F11">
-        <v>0.86656999999999995</v>
-      </c>
-      <c r="G11">
-        <v>-2</v>
-      </c>
-      <c r="H11">
-        <v>0.99475999999999998</v>
-      </c>
-      <c r="I11">
-        <v>-2</v>
-      </c>
-      <c r="J11">
-        <v>0.12747</v>
-      </c>
-      <c r="K11">
-        <v>-2</v>
-      </c>
-      <c r="L11">
-        <v>0.82855999999999996</v>
-      </c>
-      <c r="M11">
-        <v>-2</v>
-      </c>
-      <c r="N11">
-        <v>0.95130999999999999</v>
-      </c>
-      <c r="O11">
-        <v>-2</v>
-      </c>
-      <c r="P11">
-        <v>0.78354000000000001</v>
-      </c>
-      <c r="Q11">
-        <v>-2</v>
-      </c>
-      <c r="R11">
-        <v>0.26454</v>
-      </c>
-      <c r="S11">
-        <v>-2</v>
-      </c>
-      <c r="T11">
-        <v>0.91578000000000004</v>
-      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>0</v>
-      </c>
-      <c r="B12">
+      <c r="A12" s="1">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.91522000000000003</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.30146000000000001</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.97541999999999995</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.99978999999999996</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.36374000000000001</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0.98475999999999997</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0.95379999999999998</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0.63231000000000004</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0.99336000000000002</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
         <v>0.79286000000000001</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0.30146000000000001</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0.97541999999999995</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0.99978999999999996</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0.36374000000000001</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0.98475999999999997</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0.95379999999999998</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0.91522000000000003</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0.63231000000000004</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0.99336000000000002</v>
       </c>
     </row>
   </sheetData>
